--- a/data/trans_orig/IP07C19-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C19-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de burlarse de él otros chicos en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de burlarse de él otros/as chicos/as en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>553</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>586</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11432</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17891</t>
+          <t>17128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>41645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50545</t>
+          <t>50894</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>46690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57816</t>
+          <t>58020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91602</t>
+          <t>90942</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>105834</t>
+          <t>105561</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,82 +1543,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5418</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>7049</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>3830</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>12218</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>2,01%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>6050</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>7049</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>3835</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>12209</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>11748</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17789</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13661</t>
+          <t>14010</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>14540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26967</t>
+          <t>28147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66983</t>
+          <t>65798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80521</t>
+          <t>79601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68532</t>
+          <t>68363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80694</t>
+          <t>80244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>139617</t>
+          <t>139053</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>156742</t>
+          <t>157543</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>476</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9417</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>14315</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>10418</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18813</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36051</t>
+          <t>36104</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46152</t>
+          <t>46232</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43099</t>
+          <t>43309</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53247</t>
+          <t>52908</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>82191</t>
+          <t>82422</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96854</t>
+          <t>96589</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17416</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23785</t>
+          <t>23519</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14144</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21950</t>
+          <t>21147</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>17216</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31924</t>
+          <t>32666</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>48142</t>
+          <t>47534</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>61205</t>
+          <t>61211</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58417</t>
+          <t>58309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71629</t>
+          <t>70943</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>109284</t>
+          <t>109286</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>128724</t>
+          <t>128880</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11622</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13297</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>20767</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14498</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>17406</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33186</t>
+          <t>33064</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13821</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27840</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>35430</t>
+          <t>35214</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55641</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>25181</t>
+          <t>25600</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42930</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>27341</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45905</t>
+          <t>45978</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>57842</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>82446</t>
+          <t>82011</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>204744</t>
+          <t>204648</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>228519</t>
+          <t>227497</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>229238</t>
+          <t>229304</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>252661</t>
+          <t>251674</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>440002</t>
+          <t>439869</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>472974</t>
+          <t>473442</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,96%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de burlarse de él otros chicos en 2012 (tasa de respuesta: 95,41%)</t>
+          <t>Menores según la frecuencia de burlarse de él otros/as chicos/as en 2012 (tasa de respuesta: 95,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>10984</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>10387</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18429</t>
+          <t>19336</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21214</t>
+          <t>21490</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30220</t>
+          <t>30002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34997</t>
+          <t>35368</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47050</t>
+          <t>47327</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37944</t>
+          <t>36764</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50902</t>
+          <t>51266</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76813</t>
+          <t>76258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95387</t>
+          <t>94125</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14741</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>13156</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>19144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>15493</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>29100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15830</t>
+          <t>15170</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13491</t>
+          <t>13194</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>12036</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24781</t>
+          <t>25069</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>17293</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>16264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30034</t>
+          <t>29989</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57093</t>
+          <t>57496</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71855</t>
+          <t>72236</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49304</t>
+          <t>50130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64053</t>
+          <t>65312</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111411</t>
+          <t>111785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132972</t>
+          <t>132905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>16362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11683</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8014</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15825</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>13811</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10335</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22015</t>
+          <t>22360</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>10021</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21457</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30985</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43061</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39748</t>
+          <t>40635</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52629</t>
+          <t>52552</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>74916</t>
+          <t>75019</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92469</t>
+          <t>92782</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12868</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9184</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>21932</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14463</t>
+          <t>13614</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29426</t>
+          <t>28523</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16535</t>
+          <t>16073</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>14562</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29347</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42581</t>
+          <t>42324</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58464</t>
+          <t>58730</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52882</t>
+          <t>52872</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67268</t>
+          <t>67579</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>99784</t>
+          <t>100641</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>122286</t>
+          <t>121365</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>12525</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27242</t>
+          <t>26566</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20362</t>
+          <t>20922</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24123</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>42486</t>
+          <t>42610</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36963</t>
+          <t>38341</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>17118</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32600</t>
+          <t>32860</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42748</t>
+          <t>42685</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>65111</t>
+          <t>65996</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25163</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>43942</t>
+          <t>42605</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24786</t>
+          <t>24127</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>41984</t>
+          <t>43530</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>54621</t>
+          <t>53695</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>79718</t>
+          <t>79208</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27773</t>
+          <t>28287</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>47350</t>
+          <t>47809</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,82 +7457,82 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
+          <t>15,32%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>44248</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>34761</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>56285</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10,73%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>17,38%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>81005</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>67453</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>96516</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>12,74%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>10,61%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
           <t>15,17%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>44248</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>34467</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>54612</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>13,66%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>81005</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>68065</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>94895</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>12,74%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>10,7%</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>179607</t>
+          <t>177977</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>208362</t>
+          <t>208522</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>194478</t>
+          <t>195743</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>222868</t>
+          <t>223899</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>385962</t>
+          <t>383675</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>423736</t>
+          <t>424157</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,69%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de burlarse de él otros chicos en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de burlarse de él otros/as chicos/as en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13985</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>17294</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17114</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20382</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17178</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32640</t>
+          <t>33309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43540</t>
+          <t>43559</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55954</t>
+          <t>56276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35725</t>
+          <t>36057</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49975</t>
+          <t>50232</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>83574</t>
+          <t>82698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102920</t>
+          <t>102368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14539</t>
+          <t>14308</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13459</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13453</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22787</t>
+          <t>23493</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15519</t>
+          <t>15507</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28308</t>
+          <t>28269</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22251</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28364</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46353</t>
+          <t>46207</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>56837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72561</t>
+          <t>73405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58902</t>
+          <t>59746</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75020</t>
+          <t>75670</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123072</t>
+          <t>121393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>145682</t>
+          <t>143526</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>8843</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11874</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11819</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16381</t>
+          <t>15969</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24596</t>
+          <t>24019</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49190</t>
+          <t>48283</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60316</t>
+          <t>59437</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44504</t>
+          <t>45375</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58598</t>
+          <t>58942</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97368</t>
+          <t>98323</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115106</t>
+          <t>115801</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10944</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>13661</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12474</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18779</t>
+          <t>18192</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13989</t>
+          <t>13261</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21520</t>
+          <t>22364</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20831</t>
+          <t>20717</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36301</t>
+          <t>36544</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20306</t>
+          <t>19989</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35768</t>
+          <t>35598</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45009</t>
+          <t>45158</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66216</t>
+          <t>66423</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47680</t>
+          <t>48282</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>65684</t>
+          <t>65722</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48018</t>
+          <t>48607</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64437</t>
+          <t>64797</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>102790</t>
+          <t>101998</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>126635</t>
+          <t>125614</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18055</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31805</t>
+          <t>32635</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>28158</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17166</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32807</t>
+          <t>32749</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33703</t>
+          <t>33543</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55273</t>
+          <t>54864</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27257</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20370</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37942</t>
+          <t>36083</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36921</t>
+          <t>36745</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>59536</t>
+          <t>59438</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>55409</t>
+          <t>55552</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>79304</t>
+          <t>79536</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>53906</t>
+          <t>55592</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>79824</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>117663</t>
+          <t>118137</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>151282</t>
+          <t>152509</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>211873</t>
+          <t>213935</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>240816</t>
+          <t>242492</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>205872</t>
+          <t>203686</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>235914</t>
+          <t>233569</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>425035</t>
+          <t>427904</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>466564</t>
+          <t>469233</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,53%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de burlarse de él otros chicos en 2023 (tasa de respuesta: 99,65%)</t>
+          <t>Menores según la frecuencia de burlarse de él otros/as chicos/as en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>583</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>867</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>24835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30421</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36368</t>
+          <t>36860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45973</t>
+          <t>46109</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64042</t>
+          <t>64503</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75077</t>
+          <t>75178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>379</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>552</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14242</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>17622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41329</t>
+          <t>40603</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49330</t>
+          <t>49020</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85519</t>
+          <t>85720</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97472</t>
+          <t>97701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>130367</t>
+          <t>130927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>145199</t>
+          <t>145436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,2%</t>
         </is>
       </c>
     </row>
@@ -13063,7 +13063,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13324,7 +13324,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6256</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28396</t>
+          <t>28708</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59355</t>
+          <t>58951</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71027</t>
+          <t>70596</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40559</t>
+          <t>40779</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58736</t>
+          <t>58639</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104412</t>
+          <t>103970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127657</t>
+          <t>127243</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -13710,7 +13710,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -13936,7 +13936,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>877</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>165</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>13259</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>41925</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49779</t>
+          <t>50295</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44693</t>
+          <t>45038</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>53471</t>
+          <t>53435</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>89218</t>
+          <t>90316</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>101732</t>
+          <t>102059</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12159</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20187</t>
+          <t>20743</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>41089</t>
+          <t>39386</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>26155</t>
+          <t>25725</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>55357</t>
+          <t>53869</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>177918</t>
+          <t>177783</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>195923</t>
+          <t>195899</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>221063</t>
+          <t>223606</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>247439</t>
+          <t>247473</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>406842</t>
+          <t>406394</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>439575</t>
+          <t>438341</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
